--- a/Middleput/season1.xlsx
+++ b/Middleput/season1.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Goals/Game</t>
+          <t>GoalxG</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Points/Game</t>
+          <t>PointsxG</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">

--- a/Middleput/season1.xlsx
+++ b/Middleput/season1.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Daniele (Francesco)</t>
+          <t>Daniele Miccoli</t>
         </is>
       </c>
       <c r="B2" t="n">

--- a/Middleput/season1.xlsx
+++ b/Middleput/season1.xlsx
@@ -1269,49 +1269,49 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Riccardo Ricci</t>
+          <t>Matteo (Riccardo)</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7</v>
+        <v>1.71</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="N16" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="O16" t="n">
         <v>105</v>
@@ -1323,49 +1323,49 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Matteo (Riccardo)</t>
+          <t>Riccardo Ricci</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.71</v>
+        <v>0.7</v>
       </c>
       <c r="M17" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="N17" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="O17" t="n">
         <v>105</v>
@@ -2187,7 +2187,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gianluca</t>
+          <t>Matteo Virg</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2197,24 +2197,24 @@
         <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N33" t="n">
         <v>12.33</v>
@@ -2235,13 +2235,13 @@
         <v>37</v>
       </c>
       <c r="P33" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Matteo Virg</t>
+          <t>Gianluca</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2251,24 +2251,24 @@
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2277,10 +2277,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N34" t="n">
         <v>12.33</v>
@@ -2289,7 +2289,7 @@
         <v>37</v>
       </c>
       <c r="P34" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -2403,34 +2403,34 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alessandro Gibertini</t>
+          <t>Cocò (Stoppi)</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2439,52 +2439,52 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>9.33</v>
+        <v>14</v>
       </c>
       <c r="O37" t="n">
         <v>28</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cocò (Stoppi)</t>
+          <t>Alessandro Gibertini</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>36</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2493,19 +2493,19 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>14</v>
+        <v>9.33</v>
       </c>
       <c r="O38" t="n">
         <v>28</v>
       </c>
       <c r="P38" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2727,21 +2727,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Leo (Cava)</t>
+          <t>Marco Taglio</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -2754,7 +2754,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2763,39 +2763,39 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>10</v>
+        <v>6.67</v>
       </c>
       <c r="O43" t="n">
         <v>20</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Marco Taglio</t>
+          <t>Leo (Cava)</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>42</v>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2808,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2817,19 +2817,19 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>6.67</v>
+        <v>10</v>
       </c>
       <c r="O44" t="n">
         <v>20</v>
       </c>
       <c r="P44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3051,7 +3051,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Giacomo (Stoppi)</t>
+          <t>Matteo (Mazzu)</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -3078,7 +3078,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -3105,7 +3105,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Matteo (Mazzu)</t>
+          <t>Giacomo (Stoppi)</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -3132,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -3645,7 +3645,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Amico Matteo</t>
+          <t>Puddi</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -3672,7 +3672,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Puddi</t>
+          <t>Amico Matteo</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3780,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ale (Fabri)</t>
+          <t>Braz</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3861,7 +3861,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Braz</t>
+          <t>Ale (Fabri)</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -3888,7 +3888,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
